--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
@@ -1651,13 +1651,13 @@
         <v>14.15</v>
       </c>
       <c r="D8" t="n">
-        <v>12.425</v>
+        <v>12.43</v>
       </c>
       <c r="E8" t="n">
-        <v>11.625</v>
+        <v>11.62</v>
       </c>
       <c r="F8" t="n">
-        <v>12.623</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="9">
@@ -1679,7 +1679,7 @@
         <v>11.6</v>
       </c>
       <c r="F9" t="n">
-        <v>12.335</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="10">
@@ -1695,13 +1695,13 @@
         <v>12.45</v>
       </c>
       <c r="D10" t="n">
-        <v>12.425</v>
+        <v>12.43</v>
       </c>
       <c r="E10" t="n">
         <v>10.8</v>
       </c>
       <c r="F10" t="n">
-        <v>11.782</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="11">
@@ -1720,7 +1720,7 @@
         <v>15.75</v>
       </c>
       <c r="E11" t="n">
-        <v>9.125</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>11.6</v>
@@ -1742,10 +1742,10 @@
         <v>14.1</v>
       </c>
       <c r="E12" t="n">
-        <v>8.275</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>11.275</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="13">
@@ -1761,13 +1761,13 @@
         <v>10.75</v>
       </c>
       <c r="D13" t="n">
-        <v>13.275</v>
+        <v>13.28</v>
       </c>
       <c r="E13" t="n">
-        <v>9.125</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.857</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="14">
@@ -1786,7 +1786,7 @@
         <v>14.1</v>
       </c>
       <c r="E14" t="n">
-        <v>8.275</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>10.78</v>
@@ -1802,16 +1802,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.275</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>13.275</v>
+        <v>13.28</v>
       </c>
       <c r="E15" t="n">
-        <v>10.775</v>
+        <v>10.78</v>
       </c>
       <c r="F15" t="n">
-        <v>10.775</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="16">
@@ -1852,10 +1852,10 @@
         <v>8.25</v>
       </c>
       <c r="E17" t="n">
-        <v>5.775</v>
+        <v>5.78</v>
       </c>
       <c r="F17" t="n">
-        <v>6.765</v>
+        <v>6.77</v>
       </c>
     </row>
   </sheetData>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
@@ -9,7 +9,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_коллектив" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_коллектив" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +44,10 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -160,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,7 +194,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -585,12 +613,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -641,7 +669,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -658,17 +686,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -685,12 +713,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -712,7 +740,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -729,7 +757,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -746,12 +774,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -768,7 +796,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -778,7 +806,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -795,12 +823,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -812,17 +840,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -839,12 +867,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -916,12 +944,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -967,12 +995,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -989,17 +1017,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1044,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1066,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1088,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1077,7 +1105,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1099,17 +1127,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1154,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1143,17 +1171,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1198,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1270,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1298,12 +1326,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1320,17 +1348,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1342,17 +1370,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1402,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1386,17 +1414,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1436,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1440,7 +1468,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1480,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1474,17 +1502,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1496,17 +1524,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1526,336 +1554,1011 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25.29" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Четкий MoSCoW — итоговая приоритизация (коллективное решение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Веса экспертов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
           <t>Эксперт</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Вес_raw</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Вес_norm</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B5" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B6" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B8" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C8" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2) Групповая приоритизация FR методом взвешенной средней</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>PFR_MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>PFR_MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>PFR_MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>PFR_group</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="F8" t="n">
-        <v>12.62</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C12" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>20.346</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>15.994</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>15.095</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>14.072</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>13.973</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>13.585</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>10.714</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>8.613</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="E9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12.34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C20" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>7.095000000000001</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>5.912500000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1.2705</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>3) Групповая приоритизация FR с учетом взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Исходный PFR_group</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Скорректированный PFR_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>20.346</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="D10" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>11.78</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C27" s="14" t="n">
+        <v>15.994</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>15.994</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>13.973</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>15.994</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1.2705</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>15.994</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>14.072</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>14.072</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="D11" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11.28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="C31" s="14" t="n">
+        <v>13.585</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>13.585</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10.78</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="D15" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.78</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C32" s="14" t="n">
+        <v>10.714</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>10.714</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10.11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="C33" s="14" t="n">
+        <v>8.613</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>10.714</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.77</v>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>5.912500000000001</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>5.912500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_взвешенные средние.xlsx
@@ -165,15 +165,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -200,7 +200,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,6 +208,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -564,7 +567,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -579,7 +582,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -601,22 +604,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -657,220 +660,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -895,7 +898,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.5703125" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -910,7 +913,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -932,22 +935,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -988,220 +991,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1226,7 +1229,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.28515625" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -1241,7 +1244,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -1263,22 +1266,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1319,220 +1322,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1557,7 +1560,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2019,7 +2022,7 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -2030,7 +2033,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW — итоговая приоритизация (коллективное решение)</t>
+          <t>Четкий MoSCoW - итоговая приоритизация (коллективное решение, метод взвешенной средней)</t>
         </is>
       </c>
     </row>
@@ -2065,10 +2068,10 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2078,10 +2081,10 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2091,23 +2094,23 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2155,21 +2158,21 @@
       <c r="A12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="17" t="n">
         <v>22.25</v>
       </c>
     </row>
@@ -2177,21 +2180,21 @@
       <c r="A13" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>21.28</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="17" t="n">
         <v>18.78</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="17" t="n">
         <v>20.346</v>
       </c>
     </row>
@@ -2199,21 +2202,21 @@
       <c r="A14" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>15.84</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="17" t="n">
         <v>16.06</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="17" t="n">
         <v>16.06</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="17" t="n">
         <v>15.994</v>
       </c>
     </row>
@@ -2221,21 +2224,21 @@
       <c r="A15" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="17" t="n">
         <v>13.5</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="17" t="n">
         <v>15.095</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="17" t="n">
         <v>14.072</v>
       </c>
     </row>
@@ -2243,21 +2246,21 @@
       <c r="A16" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="17" t="n">
         <v>14.27</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="17" t="n">
         <v>14.27</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="17" t="n">
         <v>13.973</v>
       </c>
     </row>
@@ -2265,21 +2268,21 @@
       <c r="A17" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>13.2</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>14.19</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="17" t="n">
         <v>13.42</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="17" t="n">
         <v>13.585</v>
       </c>
     </row>
@@ -2287,21 +2290,21 @@
       <c r="A18" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>10.56</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="17" t="n">
         <v>10.714</v>
       </c>
     </row>
@@ -2309,21 +2312,21 @@
       <c r="A19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>7.92</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>8.91</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="17" t="n">
         <v>8.91</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="17" t="n">
         <v>8.613</v>
       </c>
     </row>
@@ -2331,21 +2334,21 @@
       <c r="A20" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>7.095000000000001</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="17" t="n">
         <v>5.912500000000001</v>
       </c>
     </row>
@@ -2353,21 +2356,21 @@
       <c r="A21" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="14" t="n">
+      <c r="C21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="17" t="n">
         <v>1.815</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="17" t="n">
         <v>1.815</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="17" t="n">
         <v>1.2705</v>
       </c>
     </row>
@@ -2405,15 +2408,15 @@
       <c r="A25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>22.25</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>22.25</v>
       </c>
     </row>
@@ -2421,15 +2424,15 @@
       <c r="A26" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>20.346</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>22.25</v>
       </c>
     </row>
@@ -2437,15 +2440,15 @@
       <c r="A27" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>15.994</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>15.994</v>
       </c>
     </row>
@@ -2453,15 +2456,15 @@
       <c r="A28" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>13.973</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>15.994</v>
       </c>
     </row>
@@ -2469,15 +2472,15 @@
       <c r="A29" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>1.2705</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="17" t="n">
         <v>15.994</v>
       </c>
     </row>
@@ -2485,15 +2488,15 @@
       <c r="A30" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="17" t="n">
         <v>14.072</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="17" t="n">
         <v>14.072</v>
       </c>
     </row>
@@ -2501,15 +2504,15 @@
       <c r="A31" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="17" t="n">
         <v>13.585</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="17" t="n">
         <v>13.585</v>
       </c>
     </row>
@@ -2517,15 +2520,15 @@
       <c r="A32" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="17" t="n">
         <v>10.714</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="17" t="n">
         <v>10.714</v>
       </c>
     </row>
@@ -2533,15 +2536,15 @@
       <c r="A33" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B33" s="19" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="17" t="n">
         <v>8.613</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="17" t="n">
         <v>10.714</v>
       </c>
     </row>
@@ -2549,15 +2552,15 @@
       <c r="A34" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="17" t="n">
         <v>5.912500000000001</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="17" t="n">
         <v>5.912500000000001</v>
       </c>
     </row>
